--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -1574,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822257</v>
+        <v>119821508</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,43 +1590,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552246</v>
+        <v>552046</v>
       </c>
       <c r="R10" t="n">
-        <v>7063284</v>
+        <v>7063490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1659,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,7 +1691,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119821508</v>
+        <v>119822072</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1735,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552046</v>
+        <v>552157</v>
       </c>
       <c r="R11" t="n">
-        <v>7063490</v>
+        <v>7063374</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1812,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822072</v>
+        <v>119822257</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,34 +1824,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552157</v>
+        <v>552246</v>
       </c>
       <c r="R12" t="n">
-        <v>7063374</v>
+        <v>7063284</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,12 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822321</v>
+        <v>119821832</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,39 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552253</v>
+        <v>552123</v>
       </c>
       <c r="R4" t="n">
-        <v>7063278</v>
+        <v>7063456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822704</v>
+        <v>119822640</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552066</v>
+        <v>552065</v>
       </c>
       <c r="R5" t="n">
-        <v>7063491</v>
+        <v>7063477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1111,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822095</v>
+        <v>119821980</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1156,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552188</v>
+        <v>552124</v>
       </c>
       <c r="R6" t="n">
-        <v>7063371</v>
+        <v>7063414</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1233,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119821898</v>
+        <v>119822072</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,42 +1244,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552193</v>
+        <v>552157</v>
       </c>
       <c r="R7" t="n">
-        <v>7063214</v>
+        <v>7063374</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,9 +1301,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,19 +1333,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119821499</v>
+        <v>119821659</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1380,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552067</v>
+        <v>552056</v>
       </c>
       <c r="R8" t="n">
-        <v>7063476</v>
+        <v>7063498</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1457,7 +1462,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119821659</v>
+        <v>119822383</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1497,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552056</v>
+        <v>552262</v>
       </c>
       <c r="R9" t="n">
-        <v>7063498</v>
+        <v>7063267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1691,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822072</v>
+        <v>119821898</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,37 +1712,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552157</v>
+        <v>552193</v>
       </c>
       <c r="R11" t="n">
-        <v>7063374</v>
+        <v>7063214</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,24 +1774,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,22 +1791,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822257</v>
+        <v>119822095</v>
       </c>
       <c r="B12" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,43 +1819,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552246</v>
+        <v>552188</v>
       </c>
       <c r="R12" t="n">
-        <v>7063284</v>
+        <v>7063371</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1878,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1888,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,7 +1920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119821908</v>
+        <v>119821499</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1969,13 +1960,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552131</v>
+        <v>552067</v>
       </c>
       <c r="R13" t="n">
-        <v>7063429</v>
+        <v>7063476</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2046,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119821842</v>
+        <v>119822672</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,25 +2049,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552213</v>
+        <v>552063</v>
       </c>
       <c r="R14" t="n">
-        <v>7063214</v>
+        <v>7063480</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2148,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119821609</v>
+        <v>119821760</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,43 +2155,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552085</v>
+        <v>552128</v>
       </c>
       <c r="R15" t="n">
-        <v>7063478</v>
+        <v>7063449</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2224,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822046</v>
+        <v>119821842</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,21 +2272,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2309,13 +2296,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552138</v>
+        <v>552213</v>
       </c>
       <c r="R16" t="n">
-        <v>7063369</v>
+        <v>7063214</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2342,24 +2329,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,22 +2346,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822341</v>
+        <v>119822704</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,39 +2374,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552254</v>
+        <v>552066</v>
       </c>
       <c r="R17" t="n">
-        <v>7063276</v>
+        <v>7063491</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2466,7 +2433,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2476,7 +2443,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,7 +2470,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119821980</v>
+        <v>119822321</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2537,16 +2504,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552124</v>
+        <v>552253</v>
       </c>
       <c r="R18" t="n">
-        <v>7063414</v>
+        <v>7063278</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2578,7 +2550,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2588,12 +2560,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,7 +2587,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822166</v>
+        <v>119821908</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2654,21 +2621,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552227</v>
+        <v>552131</v>
       </c>
       <c r="R19" t="n">
-        <v>7063300</v>
+        <v>7063429</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,7 +2662,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,7 +2672,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119821760</v>
+        <v>119821609</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2753,34 +2720,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552128</v>
+        <v>552085</v>
       </c>
       <c r="R20" t="n">
-        <v>7063449</v>
+        <v>7063478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2812,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2822,12 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,10 +2825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822645</v>
+        <v>119822341</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2866,38 +2837,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552065</v>
+        <v>552254</v>
       </c>
       <c r="R21" t="n">
-        <v>7063477</v>
+        <v>7063276</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2929,7 +2905,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2939,7 +2915,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,7 +2942,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822383</v>
+        <v>119822046</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -3006,10 +2982,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552262</v>
+        <v>552138</v>
       </c>
       <c r="R22" t="n">
-        <v>7063267</v>
+        <v>7063369</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3041,7 +3017,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3051,7 +3027,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3083,10 +3059,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822640</v>
+        <v>119822645</v>
       </c>
       <c r="B23" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3095,25 +3071,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3158,7 +3134,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3168,7 +3144,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3195,10 +3171,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822672</v>
+        <v>119822166</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3207,41 +3183,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552063</v>
+        <v>552227</v>
       </c>
       <c r="R24" t="n">
-        <v>7063480</v>
+        <v>7063300</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3268,9 +3249,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3285,22 +3276,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119821832</v>
+        <v>119822257</v>
       </c>
       <c r="B25" t="n">
-        <v>82305</v>
+        <v>57463</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3313,34 +3304,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552123</v>
+        <v>552246</v>
       </c>
       <c r="R25" t="n">
-        <v>7063456</v>
+        <v>7063284</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -2256,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119821842</v>
+        <v>119822704</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>91832</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,21 +2272,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552213</v>
+        <v>552066</v>
       </c>
       <c r="R16" t="n">
-        <v>7063214</v>
+        <v>7063491</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,9 +2329,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,22 +2356,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822704</v>
+        <v>119822321</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2374,34 +2384,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552066</v>
+        <v>552253</v>
       </c>
       <c r="R17" t="n">
-        <v>7063491</v>
+        <v>7063278</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2443,7 +2458,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,10 +2485,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822321</v>
+        <v>119821842</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,42 +2501,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552253</v>
+        <v>552213</v>
       </c>
       <c r="R18" t="n">
-        <v>7063278</v>
+        <v>7063214</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2548,19 +2558,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>18:09</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>18:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,12 +2575,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119821832</v>
+        <v>119821609</v>
       </c>
       <c r="B4" t="n">
-        <v>82305</v>
+        <v>57463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552123</v>
+        <v>552085</v>
       </c>
       <c r="R4" t="n">
-        <v>7063456</v>
+        <v>7063478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822640</v>
+        <v>119821842</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>79607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552065</v>
+        <v>552213</v>
       </c>
       <c r="R5" t="n">
-        <v>7063477</v>
+        <v>7063214</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,19 +1081,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>18:24</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,12 +1098,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1228,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822072</v>
+        <v>119821898</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,37 +1243,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552157</v>
+        <v>552193</v>
       </c>
       <c r="R7" t="n">
-        <v>7063374</v>
+        <v>7063214</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,24 +1305,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,19 +1322,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119821659</v>
+        <v>119822046</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1385,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552056</v>
+        <v>552138</v>
       </c>
       <c r="R8" t="n">
-        <v>7063498</v>
+        <v>7063369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1419,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1462,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822383</v>
+        <v>119822640</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>91884</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,21 +1467,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1502,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552262</v>
+        <v>552065</v>
       </c>
       <c r="R9" t="n">
-        <v>7063267</v>
+        <v>7063477</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1526,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,12 +1536,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119821508</v>
+        <v>119821832</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,21 +1579,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552046</v>
+        <v>552123</v>
       </c>
       <c r="R10" t="n">
-        <v>7063490</v>
+        <v>7063456</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,7 +1638,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,12 +1648,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119821898</v>
+        <v>119821508</v>
       </c>
       <c r="B11" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,42 +1691,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552193</v>
+        <v>552046</v>
       </c>
       <c r="R11" t="n">
-        <v>7063214</v>
+        <v>7063490</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,9 +1748,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,19 +1780,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822095</v>
+        <v>119821499</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1843,13 +1832,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552188</v>
+        <v>552067</v>
       </c>
       <c r="R12" t="n">
-        <v>7063371</v>
+        <v>7063476</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1888,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1920,7 +1909,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119821499</v>
+        <v>119822095</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1960,13 +1949,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552067</v>
+        <v>552188</v>
       </c>
       <c r="R13" t="n">
-        <v>7063476</v>
+        <v>7063371</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,7 +1984,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +1994,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2037,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822672</v>
+        <v>119821908</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,25 +2038,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2077,13 +2066,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552063</v>
+        <v>552131</v>
       </c>
       <c r="R14" t="n">
-        <v>7063480</v>
+        <v>7063429</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2110,9 +2099,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2127,22 +2131,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119821760</v>
+        <v>119822704</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,21 +2159,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2183,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552128</v>
+        <v>552066</v>
       </c>
       <c r="R15" t="n">
-        <v>7063449</v>
+        <v>7063491</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2214,7 +2218,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,12 +2228,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822704</v>
+        <v>119822341</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,34 +2271,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552066</v>
+        <v>552254</v>
       </c>
       <c r="R16" t="n">
-        <v>7063491</v>
+        <v>7063276</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2345,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,7 +2372,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822321</v>
+        <v>119821760</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2402,21 +2406,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552253</v>
+        <v>552128</v>
       </c>
       <c r="R17" t="n">
-        <v>7063278</v>
+        <v>7063449</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,7 +2457,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119821842</v>
+        <v>119822383</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,21 +2505,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2525,13 +2529,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552213</v>
+        <v>552262</v>
       </c>
       <c r="R18" t="n">
-        <v>7063214</v>
+        <v>7063267</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2558,9 +2562,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,22 +2594,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119821908</v>
+        <v>119822672</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,25 +2618,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2627,13 +2646,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552131</v>
+        <v>552063</v>
       </c>
       <c r="R19" t="n">
-        <v>7063429</v>
+        <v>7063480</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2660,24 +2679,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2692,22 +2696,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119821609</v>
+        <v>119822645</v>
       </c>
       <c r="B20" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,47 +2720,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552085</v>
+        <v>552065</v>
       </c>
       <c r="R20" t="n">
-        <v>7063478</v>
+        <v>7063477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2788,7 +2783,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2793,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,7 +2820,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822341</v>
+        <v>119822072</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -2859,21 +2854,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552254</v>
+        <v>552157</v>
       </c>
       <c r="R21" t="n">
-        <v>7063276</v>
+        <v>7063374</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,7 +2895,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,7 +2905,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,7 +2937,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822046</v>
+        <v>119822166</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2976,16 +2971,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552138</v>
+        <v>552227</v>
       </c>
       <c r="R22" t="n">
-        <v>7063369</v>
+        <v>7063300</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3027,12 +3027,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3059,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822645</v>
+        <v>119822257</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3071,38 +3066,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552065</v>
+        <v>552246</v>
       </c>
       <c r="R23" t="n">
-        <v>7063477</v>
+        <v>7063284</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3134,7 +3138,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3144,7 +3148,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3171,7 +3175,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822166</v>
+        <v>119821659</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3205,21 +3209,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552227</v>
+        <v>552056</v>
       </c>
       <c r="R24" t="n">
-        <v>7063300</v>
+        <v>7063498</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,7 +3250,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3261,7 +3260,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3288,10 +3292,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822257</v>
+        <v>119822321</v>
       </c>
       <c r="B25" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3304,31 +3308,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552246</v>
+        <v>552253</v>
       </c>
       <c r="R25" t="n">
-        <v>7063284</v>
+        <v>7063278</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119821609</v>
+        <v>119822095</v>
       </c>
       <c r="B4" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,43 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552085</v>
+        <v>552188</v>
       </c>
       <c r="R4" t="n">
-        <v>7063478</v>
+        <v>7063371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +972,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119821842</v>
+        <v>119821659</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,13 +1044,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552213</v>
+        <v>552056</v>
       </c>
       <c r="R5" t="n">
-        <v>7063214</v>
+        <v>7063498</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,9 +1077,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,19 +1109,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119821980</v>
+        <v>119822341</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1144,16 +1155,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552124</v>
+        <v>552254</v>
       </c>
       <c r="R6" t="n">
-        <v>7063414</v>
+        <v>7063276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,12 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119821898</v>
+        <v>119821508</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,42 +1254,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552193</v>
+        <v>552046</v>
       </c>
       <c r="R7" t="n">
-        <v>7063214</v>
+        <v>7063490</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,9 +1311,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,22 +1343,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822046</v>
+        <v>119821832</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552138</v>
+        <v>552123</v>
       </c>
       <c r="R8" t="n">
-        <v>7063369</v>
+        <v>7063456</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1419,12 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822640</v>
+        <v>119822383</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,21 +1483,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552065</v>
+        <v>552262</v>
       </c>
       <c r="R9" t="n">
-        <v>7063477</v>
+        <v>7063267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1536,7 +1552,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119821832</v>
+        <v>119821980</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1600,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552123</v>
+        <v>552124</v>
       </c>
       <c r="R10" t="n">
-        <v>7063456</v>
+        <v>7063414</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1648,7 +1669,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119821508</v>
+        <v>119821898</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,37 +1717,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552046</v>
+        <v>552193</v>
       </c>
       <c r="R11" t="n">
-        <v>7063490</v>
+        <v>7063214</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,24 +1779,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,19 +1796,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119821499</v>
+        <v>119822321</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1826,19 +1842,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552067</v>
+        <v>552253</v>
       </c>
       <c r="R12" t="n">
-        <v>7063476</v>
+        <v>7063278</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,12 +1898,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,7 +1925,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822095</v>
+        <v>119821760</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1949,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552188</v>
+        <v>552128</v>
       </c>
       <c r="R13" t="n">
-        <v>7063371</v>
+        <v>7063449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1984,7 +2000,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1994,7 +2010,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2026,7 +2042,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119821908</v>
+        <v>119822072</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -2066,10 +2082,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552131</v>
+        <v>552157</v>
       </c>
       <c r="R14" t="n">
-        <v>7063429</v>
+        <v>7063374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2111,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2143,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822704</v>
+        <v>119821842</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,21 +2175,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2183,13 +2199,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552066</v>
+        <v>552213</v>
       </c>
       <c r="R15" t="n">
-        <v>7063491</v>
+        <v>7063214</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2216,19 +2232,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>18:32</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>18:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,22 +2249,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822341</v>
+        <v>119822645</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2267,43 +2273,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552254</v>
+        <v>552065</v>
       </c>
       <c r="R16" t="n">
-        <v>7063276</v>
+        <v>7063477</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2336,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2345,7 +2346,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2372,10 +2373,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119821760</v>
+        <v>119822672</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,25 +2385,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2412,13 +2413,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552128</v>
+        <v>552063</v>
       </c>
       <c r="R17" t="n">
-        <v>7063449</v>
+        <v>7063480</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2445,24 +2446,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:38</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,19 +2463,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822383</v>
+        <v>119821908</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2529,10 +2515,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552262</v>
+        <v>552131</v>
       </c>
       <c r="R18" t="n">
-        <v>7063267</v>
+        <v>7063429</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,7 +2550,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,7 +2560,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2606,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822672</v>
+        <v>119822257</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2618,41 +2604,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552063</v>
+        <v>552246</v>
       </c>
       <c r="R19" t="n">
-        <v>7063480</v>
+        <v>7063284</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2679,9 +2674,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,22 +2701,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822645</v>
+        <v>119821499</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2720,25 +2725,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2748,13 +2753,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552065</v>
+        <v>552067</v>
       </c>
       <c r="R20" t="n">
-        <v>7063477</v>
+        <v>7063476</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2783,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2793,7 +2798,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2820,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822072</v>
+        <v>119822704</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,21 +2846,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,10 +2870,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552157</v>
+        <v>552066</v>
       </c>
       <c r="R21" t="n">
-        <v>7063374</v>
+        <v>7063491</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,7 +2905,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2905,12 +2915,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3054,7 +3059,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822257</v>
+        <v>119821609</v>
       </c>
       <c r="B23" t="n">
         <v>57463</v>
@@ -3103,10 +3108,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552246</v>
+        <v>552085</v>
       </c>
       <c r="R23" t="n">
-        <v>7063284</v>
+        <v>7063478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,7 +3143,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3148,7 +3153,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3175,10 +3180,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119821659</v>
+        <v>119822640</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>91884</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3191,21 +3196,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3215,10 +3220,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552056</v>
+        <v>552065</v>
       </c>
       <c r="R24" t="n">
-        <v>7063498</v>
+        <v>7063477</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,7 +3255,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3260,12 +3265,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3292,7 +3292,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822321</v>
+        <v>119822046</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3326,21 +3326,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552253</v>
+        <v>552138</v>
       </c>
       <c r="R25" t="n">
-        <v>7063278</v>
+        <v>7063369</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3372,7 +3367,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3382,7 +3377,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119821832</v>
+        <v>119822383</v>
       </c>
       <c r="B8" t="n">
-        <v>82305</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552123</v>
+        <v>552262</v>
       </c>
       <c r="R8" t="n">
-        <v>7063456</v>
+        <v>7063267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1440,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822383</v>
+        <v>119821832</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,21 +1488,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552262</v>
+        <v>552123</v>
       </c>
       <c r="R9" t="n">
-        <v>7063267</v>
+        <v>7063456</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,12 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822072</v>
+        <v>119821842</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,21 +2058,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2082,13 +2082,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552157</v>
+        <v>552213</v>
       </c>
       <c r="R14" t="n">
-        <v>7063374</v>
+        <v>7063214</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2115,24 +2115,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,22 +2132,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119821842</v>
+        <v>119822645</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,25 +2156,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2199,13 +2184,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552213</v>
+        <v>552065</v>
       </c>
       <c r="R15" t="n">
-        <v>7063214</v>
+        <v>7063477</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2232,9 +2217,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,22 +2244,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822645</v>
+        <v>119822072</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,25 +2268,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2301,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552065</v>
+        <v>552157</v>
       </c>
       <c r="R16" t="n">
-        <v>7063477</v>
+        <v>7063374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2346,7 +2341,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822257</v>
+        <v>119822704</v>
       </c>
       <c r="B19" t="n">
-        <v>57463</v>
+        <v>91832</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2608,43 +2608,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552246</v>
+        <v>552066</v>
       </c>
       <c r="R19" t="n">
-        <v>7063284</v>
+        <v>7063491</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2686,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2713,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119821499</v>
+        <v>119822257</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,37 +2720,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552067</v>
+        <v>552246</v>
       </c>
       <c r="R20" t="n">
-        <v>7063476</v>
+        <v>7063284</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,12 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2830,10 +2825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822704</v>
+        <v>119821499</v>
       </c>
       <c r="B21" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2846,21 +2841,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2870,13 +2865,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552066</v>
+        <v>552067</v>
       </c>
       <c r="R21" t="n">
-        <v>7063491</v>
+        <v>7063476</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2905,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,7 +2910,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822383</v>
+        <v>119821832</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552262</v>
+        <v>552123</v>
       </c>
       <c r="R8" t="n">
-        <v>7063267</v>
+        <v>7063456</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,12 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119821832</v>
+        <v>119822383</v>
       </c>
       <c r="B9" t="n">
-        <v>82305</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,21 +1483,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1512,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552123</v>
+        <v>552262</v>
       </c>
       <c r="R9" t="n">
-        <v>7063456</v>
+        <v>7063267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1552,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119821842</v>
+        <v>119822072</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,21 +2058,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2082,13 +2082,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552213</v>
+        <v>552157</v>
       </c>
       <c r="R14" t="n">
-        <v>7063214</v>
+        <v>7063374</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2115,9 +2115,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,22 +2147,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822645</v>
+        <v>119821842</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,25 +2171,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2184,13 +2199,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552065</v>
+        <v>552213</v>
       </c>
       <c r="R15" t="n">
-        <v>7063477</v>
+        <v>7063214</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2217,19 +2232,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>18:25</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>18:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2244,22 +2249,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822072</v>
+        <v>119822645</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,25 +2273,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2296,10 +2301,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552157</v>
+        <v>552065</v>
       </c>
       <c r="R16" t="n">
-        <v>7063374</v>
+        <v>7063477</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2336,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,12 +2346,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3059,10 +3059,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119821609</v>
+        <v>119822046</v>
       </c>
       <c r="B23" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3075,43 +3075,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552085</v>
+        <v>552138</v>
       </c>
       <c r="R23" t="n">
-        <v>7063478</v>
+        <v>7063369</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3143,7 +3134,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3153,7 +3144,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3292,10 +3288,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822046</v>
+        <v>119821609</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3308,34 +3304,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552138</v>
+        <v>552085</v>
       </c>
       <c r="R25" t="n">
-        <v>7063369</v>
+        <v>7063478</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3367,7 +3372,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3377,12 +3382,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -2042,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822072</v>
+        <v>119821842</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,21 +2058,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2082,13 +2082,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552157</v>
+        <v>552213</v>
       </c>
       <c r="R14" t="n">
-        <v>7063374</v>
+        <v>7063214</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2115,24 +2115,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,22 +2132,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119821842</v>
+        <v>119822645</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,25 +2156,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2199,13 +2184,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552213</v>
+        <v>552065</v>
       </c>
       <c r="R15" t="n">
-        <v>7063214</v>
+        <v>7063477</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2232,9 +2217,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,22 +2244,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822645</v>
+        <v>119822072</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,25 +2268,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2301,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552065</v>
+        <v>552157</v>
       </c>
       <c r="R16" t="n">
-        <v>7063477</v>
+        <v>7063374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2346,7 +2341,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3059,10 +3059,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822046</v>
+        <v>119821609</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3075,34 +3075,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552138</v>
+        <v>552085</v>
       </c>
       <c r="R23" t="n">
-        <v>7063369</v>
+        <v>7063478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3134,7 +3143,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3144,12 +3153,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3288,10 +3292,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119821609</v>
+        <v>119822046</v>
       </c>
       <c r="B25" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3304,43 +3308,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552085</v>
+        <v>552138</v>
       </c>
       <c r="R25" t="n">
-        <v>7063478</v>
+        <v>7063369</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3372,7 +3367,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3382,7 +3377,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119821832</v>
+        <v>119822383</v>
       </c>
       <c r="B8" t="n">
-        <v>82305</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552123</v>
+        <v>552262</v>
       </c>
       <c r="R8" t="n">
-        <v>7063456</v>
+        <v>7063267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1440,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822383</v>
+        <v>119821832</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,21 +1488,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552262</v>
+        <v>552123</v>
       </c>
       <c r="R9" t="n">
-        <v>7063267</v>
+        <v>7063456</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,12 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822095</v>
+        <v>119822072</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552188</v>
+        <v>552157</v>
       </c>
       <c r="R4" t="n">
-        <v>7063371</v>
+        <v>7063374</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1007,7 +1007,7 @@
         <v>119821659</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822341</v>
+        <v>119821842</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,42 +1137,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552254</v>
+        <v>552213</v>
       </c>
       <c r="R6" t="n">
-        <v>7063276</v>
+        <v>7063214</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,19 +1194,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>18:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,22 +1211,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119821508</v>
+        <v>119821499</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,13 +1263,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552046</v>
+        <v>552067</v>
       </c>
       <c r="R7" t="n">
-        <v>7063490</v>
+        <v>7063476</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1308,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1355,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822383</v>
+        <v>119822257</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,34 +1356,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552262</v>
+        <v>552246</v>
       </c>
       <c r="R8" t="n">
-        <v>7063267</v>
+        <v>7063284</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,12 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119821832</v>
+        <v>119822166</v>
       </c>
       <c r="B9" t="n">
-        <v>82305</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,34 +1477,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552123</v>
+        <v>552227</v>
       </c>
       <c r="R9" t="n">
-        <v>7063456</v>
+        <v>7063300</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119821980</v>
+        <v>119822383</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552124</v>
+        <v>552262</v>
       </c>
       <c r="R10" t="n">
-        <v>7063414</v>
+        <v>7063267</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1701,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119821898</v>
+        <v>119822321</v>
       </c>
       <c r="B11" t="n">
-        <v>57463</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,27 +1711,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1746,13 +1740,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552193</v>
+        <v>552253</v>
       </c>
       <c r="R11" t="n">
-        <v>7063214</v>
+        <v>7063278</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,9 +1773,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,22 +1800,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822321</v>
+        <v>119821609</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,27 +1828,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1853,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552253</v>
+        <v>552085</v>
       </c>
       <c r="R12" t="n">
-        <v>7063278</v>
+        <v>7063478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119821760</v>
+        <v>119822095</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1965,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552128</v>
+        <v>552188</v>
       </c>
       <c r="R13" t="n">
-        <v>7063449</v>
+        <v>7063371</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2010,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2042,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119821842</v>
+        <v>119821908</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,21 +2066,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2082,13 +2090,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552213</v>
+        <v>552131</v>
       </c>
       <c r="R14" t="n">
-        <v>7063214</v>
+        <v>7063429</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2115,9 +2123,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,12 +2155,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2147,7 +2170,7 @@
         <v>119822645</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2256,10 +2279,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822072</v>
+        <v>119821898</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,37 +2295,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552157</v>
+        <v>552193</v>
       </c>
       <c r="R16" t="n">
-        <v>7063374</v>
+        <v>7063214</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,24 +2357,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,22 +2374,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822672</v>
+        <v>119821760</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2385,25 +2398,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2413,13 +2426,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552063</v>
+        <v>552128</v>
       </c>
       <c r="R17" t="n">
-        <v>7063480</v>
+        <v>7063449</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2446,9 +2459,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,22 +2491,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119821908</v>
+        <v>119822046</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,10 +2543,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552131</v>
+        <v>552138</v>
       </c>
       <c r="R18" t="n">
-        <v>7063429</v>
+        <v>7063369</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2550,7 +2578,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2560,7 +2588,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2592,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822704</v>
+        <v>119822640</v>
       </c>
       <c r="B19" t="n">
-        <v>91832</v>
+        <v>91902</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2608,21 +2636,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2660,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552066</v>
+        <v>552065</v>
       </c>
       <c r="R19" t="n">
-        <v>7063491</v>
+        <v>7063477</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2695,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2705,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2732,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822257</v>
+        <v>119822704</v>
       </c>
       <c r="B20" t="n">
-        <v>57463</v>
+        <v>91850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2720,43 +2748,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552246</v>
+        <v>552066</v>
       </c>
       <c r="R20" t="n">
-        <v>7063284</v>
+        <v>7063491</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2788,7 +2807,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2817,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,10 +2844,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119821499</v>
+        <v>119822341</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2859,19 +2878,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552067</v>
+        <v>552254</v>
       </c>
       <c r="R21" t="n">
-        <v>7063476</v>
+        <v>7063276</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2900,7 +2924,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,12 +2934,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,10 +2961,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822166</v>
+        <v>119821508</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2976,21 +2995,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552227</v>
+        <v>552046</v>
       </c>
       <c r="R22" t="n">
-        <v>7063300</v>
+        <v>7063490</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3022,7 +3036,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3032,7 +3046,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3059,10 +3078,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119821609</v>
+        <v>119821832</v>
       </c>
       <c r="B23" t="n">
-        <v>57463</v>
+        <v>82321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3075,43 +3094,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552085</v>
+        <v>552123</v>
       </c>
       <c r="R23" t="n">
-        <v>7063478</v>
+        <v>7063456</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3143,7 +3153,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3153,7 +3163,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3180,10 +3190,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822640</v>
+        <v>119821980</v>
       </c>
       <c r="B24" t="n">
-        <v>91884</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3196,21 +3206,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3220,10 +3230,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552065</v>
+        <v>552124</v>
       </c>
       <c r="R24" t="n">
-        <v>7063477</v>
+        <v>7063414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3255,7 +3265,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3265,7 +3275,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3292,10 +3307,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822046</v>
+        <v>119822672</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3304,25 +3319,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3332,13 +3347,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552138</v>
+        <v>552063</v>
       </c>
       <c r="R25" t="n">
-        <v>7063369</v>
+        <v>7063480</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3365,24 +3380,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3397,12 +3397,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -1933,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822095</v>
+        <v>119821898</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,37 +1949,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552188</v>
+        <v>552193</v>
       </c>
       <c r="R13" t="n">
-        <v>7063371</v>
+        <v>7063214</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2006,24 +2011,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,19 +2028,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119821908</v>
+        <v>119822095</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2090,10 +2080,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552131</v>
+        <v>552188</v>
       </c>
       <c r="R14" t="n">
-        <v>7063429</v>
+        <v>7063371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2115,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2135,7 +2125,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2167,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822645</v>
+        <v>119821908</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,25 +2169,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552065</v>
+        <v>552131</v>
       </c>
       <c r="R15" t="n">
-        <v>7063477</v>
+        <v>7063429</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2252,7 +2242,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119821898</v>
+        <v>119822645</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,46 +2286,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552193</v>
+        <v>552065</v>
       </c>
       <c r="R16" t="n">
-        <v>7063214</v>
+        <v>7063477</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2357,9 +2347,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,12 +2374,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822704</v>
+        <v>119822341</v>
       </c>
       <c r="B20" t="n">
-        <v>91850</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2748,34 +2748,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552066</v>
+        <v>552254</v>
       </c>
       <c r="R20" t="n">
-        <v>7063491</v>
+        <v>7063276</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2807,7 +2812,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2817,7 +2822,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,10 +2849,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822341</v>
+        <v>119822704</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>91850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2860,39 +2865,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552254</v>
+        <v>552066</v>
       </c>
       <c r="R21" t="n">
-        <v>7063276</v>
+        <v>7063491</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822072</v>
+        <v>119822257</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552157</v>
+        <v>552246</v>
       </c>
       <c r="R4" t="n">
-        <v>7063374</v>
+        <v>7063284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,12 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119821659</v>
+        <v>119822672</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552056</v>
+        <v>552063</v>
       </c>
       <c r="R5" t="n">
-        <v>7063498</v>
+        <v>7063480</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,24 +1081,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:29</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,22 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119821842</v>
+        <v>119822095</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552213</v>
+        <v>552188</v>
       </c>
       <c r="R6" t="n">
-        <v>7063214</v>
+        <v>7063371</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,9 +1183,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,19 +1215,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119821499</v>
+        <v>119822166</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1257,19 +1261,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552067</v>
+        <v>552227</v>
       </c>
       <c r="R7" t="n">
-        <v>7063476</v>
+        <v>7063300</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,12 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822257</v>
+        <v>119822046</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,43 +1360,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552246</v>
+        <v>552138</v>
       </c>
       <c r="R8" t="n">
-        <v>7063284</v>
+        <v>7063369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1429,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,7 +1461,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822166</v>
+        <v>119821499</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1495,24 +1495,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552227</v>
+        <v>552067</v>
       </c>
       <c r="R9" t="n">
-        <v>7063300</v>
+        <v>7063476</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1546,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822383</v>
+        <v>119822704</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>91850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,21 +1594,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552262</v>
+        <v>552066</v>
       </c>
       <c r="R10" t="n">
-        <v>7063267</v>
+        <v>7063491</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,12 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,7 +1690,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822321</v>
+        <v>119821508</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1729,21 +1724,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552253</v>
+        <v>552046</v>
       </c>
       <c r="R11" t="n">
-        <v>7063278</v>
+        <v>7063490</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1785,7 +1775,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119821609</v>
+        <v>119821760</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,43 +1823,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552085</v>
+        <v>552128</v>
       </c>
       <c r="R12" t="n">
-        <v>7063478</v>
+        <v>7063449</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1892,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119821898</v>
+        <v>119822072</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,42 +1940,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552193</v>
+        <v>552157</v>
       </c>
       <c r="R13" t="n">
-        <v>7063214</v>
+        <v>7063374</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,9 +1997,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,19 +2029,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822095</v>
+        <v>119822321</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2074,16 +2075,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552188</v>
+        <v>552253</v>
       </c>
       <c r="R14" t="n">
-        <v>7063371</v>
+        <v>7063278</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2125,12 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119821908</v>
+        <v>119822645</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,25 +2170,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2197,10 +2198,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552131</v>
+        <v>552065</v>
       </c>
       <c r="R15" t="n">
-        <v>7063429</v>
+        <v>7063477</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,12 +2243,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2270,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822645</v>
+        <v>119821898</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,41 +2282,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552065</v>
+        <v>552193</v>
       </c>
       <c r="R16" t="n">
-        <v>7063477</v>
+        <v>7063214</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2347,19 +2348,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>18:25</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>18:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,19 +2365,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119821760</v>
+        <v>119821908</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2426,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552128</v>
+        <v>552131</v>
       </c>
       <c r="R17" t="n">
-        <v>7063449</v>
+        <v>7063429</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2462,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2503,7 +2494,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822046</v>
+        <v>119822341</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2537,16 +2528,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552138</v>
+        <v>552254</v>
       </c>
       <c r="R18" t="n">
-        <v>7063369</v>
+        <v>7063276</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2578,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2588,12 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822640</v>
+        <v>119822383</v>
       </c>
       <c r="B19" t="n">
-        <v>91902</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,21 +2627,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2660,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552065</v>
+        <v>552262</v>
       </c>
       <c r="R19" t="n">
-        <v>7063477</v>
+        <v>7063267</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2695,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2705,7 +2696,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2732,10 +2728,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822341</v>
+        <v>119821832</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2748,39 +2744,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552254</v>
+        <v>552123</v>
       </c>
       <c r="R20" t="n">
-        <v>7063276</v>
+        <v>7063456</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2812,7 +2803,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2822,7 +2813,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2849,10 +2840,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822704</v>
+        <v>119821609</v>
       </c>
       <c r="B21" t="n">
-        <v>91850</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2865,34 +2856,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552066</v>
+        <v>552085</v>
       </c>
       <c r="R21" t="n">
-        <v>7063491</v>
+        <v>7063478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2961,10 +2961,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119821508</v>
+        <v>119822640</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>91902</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552046</v>
+        <v>552065</v>
       </c>
       <c r="R22" t="n">
-        <v>7063490</v>
+        <v>7063477</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3046,12 +3046,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3078,10 +3073,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119821832</v>
+        <v>119821842</v>
       </c>
       <c r="B23" t="n">
-        <v>82321</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3094,21 +3089,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3118,13 +3113,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552123</v>
+        <v>552213</v>
       </c>
       <c r="R23" t="n">
-        <v>7063456</v>
+        <v>7063214</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3151,19 +3146,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>17:43</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>17:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3178,12 +3163,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3307,10 +3292,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822672</v>
+        <v>119821659</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3319,25 +3304,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3347,13 +3332,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552063</v>
+        <v>552056</v>
       </c>
       <c r="R25" t="n">
-        <v>7063480</v>
+        <v>7063498</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3380,9 +3365,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3397,12 +3397,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119821499</v>
+        <v>119822704</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>91850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552067</v>
+        <v>552066</v>
       </c>
       <c r="R9" t="n">
-        <v>7063476</v>
+        <v>7063491</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1546,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822704</v>
+        <v>119821499</v>
       </c>
       <c r="B10" t="n">
-        <v>91850</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,21 +1589,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1618,13 +1613,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552066</v>
+        <v>552067</v>
       </c>
       <c r="R10" t="n">
-        <v>7063491</v>
+        <v>7063476</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,7 +1648,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1658,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2961,10 +2961,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822640</v>
+        <v>119821980</v>
       </c>
       <c r="B22" t="n">
-        <v>91902</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552065</v>
+        <v>552124</v>
       </c>
       <c r="R22" t="n">
-        <v>7063477</v>
+        <v>7063414</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3046,7 +3046,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3073,10 +3078,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119821842</v>
+        <v>119821659</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3089,21 +3094,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3113,13 +3118,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552213</v>
+        <v>552056</v>
       </c>
       <c r="R23" t="n">
-        <v>7063214</v>
+        <v>7063498</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3146,9 +3151,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,22 +3183,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119821980</v>
+        <v>119822640</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>91902</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3191,21 +3211,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3215,10 +3235,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552124</v>
+        <v>552065</v>
       </c>
       <c r="R24" t="n">
-        <v>7063414</v>
+        <v>7063477</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,7 +3270,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3260,12 +3280,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3292,10 +3307,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119821659</v>
+        <v>119821842</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3308,21 +3323,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3332,13 +3347,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552056</v>
+        <v>552213</v>
       </c>
       <c r="R25" t="n">
-        <v>7063498</v>
+        <v>7063214</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3365,24 +3380,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>17:29</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3397,12 +3397,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822257</v>
+        <v>119822095</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,43 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552246</v>
+        <v>552188</v>
       </c>
       <c r="R4" t="n">
-        <v>7063284</v>
+        <v>7063371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +972,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822672</v>
+        <v>119822341</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,41 +1016,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552063</v>
+        <v>552254</v>
       </c>
       <c r="R5" t="n">
-        <v>7063480</v>
+        <v>7063276</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,9 +1082,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,19 +1109,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822095</v>
+        <v>119821760</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1150,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552188</v>
+        <v>552128</v>
       </c>
       <c r="R6" t="n">
-        <v>7063371</v>
+        <v>7063449</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1344,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822046</v>
+        <v>119822645</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,25 +1367,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1384,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552138</v>
+        <v>552065</v>
       </c>
       <c r="R8" t="n">
-        <v>7063369</v>
+        <v>7063477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,12 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822704</v>
+        <v>119821898</v>
       </c>
       <c r="B9" t="n">
-        <v>91850</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,37 +1483,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552066</v>
+        <v>552193</v>
       </c>
       <c r="R9" t="n">
-        <v>7063491</v>
+        <v>7063214</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,19 +1545,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:32</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,19 +1562,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119821499</v>
+        <v>119821508</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1613,13 +1614,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552067</v>
+        <v>552046</v>
       </c>
       <c r="R10" t="n">
-        <v>7063476</v>
+        <v>7063490</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1648,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1658,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1690,7 +1691,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119821508</v>
+        <v>119822321</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1724,16 +1725,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552046</v>
+        <v>552253</v>
       </c>
       <c r="R11" t="n">
-        <v>7063490</v>
+        <v>7063278</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,12 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119821760</v>
+        <v>119821832</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,21 +1824,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1847,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552128</v>
+        <v>552123</v>
       </c>
       <c r="R12" t="n">
-        <v>7063449</v>
+        <v>7063456</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,12 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,7 +1920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822072</v>
+        <v>119822383</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1964,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552157</v>
+        <v>552262</v>
       </c>
       <c r="R13" t="n">
-        <v>7063374</v>
+        <v>7063267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2009,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2041,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822321</v>
+        <v>119822672</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,46 +2049,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552253</v>
+        <v>552063</v>
       </c>
       <c r="R14" t="n">
-        <v>7063278</v>
+        <v>7063480</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2119,19 +2110,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>18:09</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>18:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,22 +2127,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822645</v>
+        <v>119822640</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,25 +2151,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2233,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2243,7 +2224,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,10 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119821898</v>
+        <v>119822046</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,42 +2267,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552193</v>
+        <v>552138</v>
       </c>
       <c r="R16" t="n">
-        <v>7063214</v>
+        <v>7063369</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2348,9 +2324,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,22 +2356,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119821908</v>
+        <v>119821842</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,21 +2384,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2417,13 +2408,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552131</v>
+        <v>552213</v>
       </c>
       <c r="R17" t="n">
-        <v>7063429</v>
+        <v>7063214</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2450,24 +2441,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,22 +2458,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822341</v>
+        <v>119822704</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>91850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,39 +2486,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552254</v>
+        <v>552066</v>
       </c>
       <c r="R18" t="n">
-        <v>7063276</v>
+        <v>7063491</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,7 +2545,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2555,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,7 +2582,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822383</v>
+        <v>119822072</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2651,10 +2622,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552262</v>
+        <v>552157</v>
       </c>
       <c r="R19" t="n">
-        <v>7063267</v>
+        <v>7063374</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2686,7 +2657,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2696,7 +2667,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2728,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119821832</v>
+        <v>119821980</v>
       </c>
       <c r="B20" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,21 +2715,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2768,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552123</v>
+        <v>552124</v>
       </c>
       <c r="R20" t="n">
-        <v>7063456</v>
+        <v>7063414</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,7 +2774,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2813,7 +2784,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2961,7 +2937,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119821980</v>
+        <v>119821908</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -3001,10 +2977,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552124</v>
+        <v>552131</v>
       </c>
       <c r="R22" t="n">
-        <v>7063414</v>
+        <v>7063429</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,7 +3012,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3046,7 +3022,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3078,7 +3054,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119821659</v>
+        <v>119821499</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -3118,13 +3094,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552056</v>
+        <v>552067</v>
       </c>
       <c r="R23" t="n">
-        <v>7063498</v>
+        <v>7063476</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3153,7 +3129,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3163,7 +3139,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3195,10 +3171,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822640</v>
+        <v>119822257</v>
       </c>
       <c r="B24" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3211,34 +3187,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552065</v>
+        <v>552246</v>
       </c>
       <c r="R24" t="n">
-        <v>7063477</v>
+        <v>7063284</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3270,7 +3255,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3280,7 +3265,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3307,10 +3292,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119821842</v>
+        <v>119821659</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3323,21 +3308,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3347,13 +3332,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552213</v>
+        <v>552056</v>
       </c>
       <c r="R25" t="n">
-        <v>7063214</v>
+        <v>7063498</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3380,9 +3365,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3397,12 +3397,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 33121-2024 artfynd.xlsx
+++ b/artfynd/A 33121-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>112892609</v>
       </c>
       <c r="B2" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112892617</v>
+        <v>119821832</v>
       </c>
       <c r="B3" t="n">
-        <v>74202</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,40 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brattfors, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552278</v>
+        <v>552123</v>
       </c>
       <c r="R3" t="n">
-        <v>7063319</v>
+        <v>7063456</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,34 +865,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822095</v>
+        <v>119822688</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552188</v>
+        <v>552038</v>
       </c>
       <c r="R4" t="n">
-        <v>7063371</v>
+        <v>7063491</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,24 +951,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,27 +968,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822341</v>
+        <v>119822704</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,39 +991,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552254</v>
+        <v>552066</v>
       </c>
       <c r="R5" t="n">
-        <v>7063276</v>
+        <v>7063491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1050,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1060,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,15 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119821760</v>
+        <v>119822645</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552128</v>
+        <v>552065</v>
       </c>
       <c r="R6" t="n">
-        <v>7063449</v>
+        <v>7063477</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1157,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,12 +1167,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,15 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822166</v>
+        <v>119822672</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,42 +1205,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552227</v>
+        <v>552063</v>
       </c>
       <c r="R7" t="n">
-        <v>7063300</v>
+        <v>7063480</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,19 +1262,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,65 +1279,63 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822645</v>
+        <v>112892617</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Brattfors, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552065</v>
+        <v>552278</v>
       </c>
       <c r="R8" t="n">
-        <v>7063477</v>
+        <v>7063319</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,22 +1359,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:25</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:25</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,33 +1373,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119821898</v>
+        <v>119821842</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,42 +1403,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552193</v>
+        <v>552213</v>
       </c>
       <c r="R9" t="n">
         <v>7063214</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,15 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119821508</v>
+        <v>119821499</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,13 +1524,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552046</v>
+        <v>552067</v>
       </c>
       <c r="R10" t="n">
-        <v>7063490</v>
+        <v>7063476</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,7 +1559,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1569,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1691,15 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822321</v>
+        <v>119821508</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,21 +1630,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552253</v>
+        <v>552046</v>
       </c>
       <c r="R11" t="n">
-        <v>7063278</v>
+        <v>7063490</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1671,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1681,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,15 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119821832</v>
+        <v>119821659</v>
       </c>
       <c r="B12" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,21 +1724,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552123</v>
+        <v>552056</v>
       </c>
       <c r="R12" t="n">
-        <v>7063456</v>
+        <v>7063498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1783,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1793,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,15 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822383</v>
+        <v>119821760</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552262</v>
+        <v>552128</v>
       </c>
       <c r="R13" t="n">
-        <v>7063267</v>
+        <v>7063449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1895,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +1905,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2037,37 +1937,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822672</v>
+        <v>119821908</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2077,13 +1972,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552063</v>
+        <v>552131</v>
       </c>
       <c r="R14" t="n">
-        <v>7063480</v>
+        <v>7063429</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2110,9 +2005,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2127,27 +2037,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822640</v>
+        <v>119821980</v>
       </c>
       <c r="B15" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,21 +2060,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2084,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552065</v>
+        <v>552124</v>
       </c>
       <c r="R15" t="n">
-        <v>7063477</v>
+        <v>7063414</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2214,7 +2119,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,7 +2129,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,12 +2164,7 @@
         <v>119822046</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,15 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119821842</v>
+        <v>119822072</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2384,21 +2284,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2408,13 +2308,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552213</v>
+        <v>552157</v>
       </c>
       <c r="R17" t="n">
-        <v>7063214</v>
+        <v>7063374</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2441,9 +2341,24 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,27 +2373,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822704</v>
+        <v>119822095</v>
       </c>
       <c r="B18" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,21 +2396,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2510,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552066</v>
+        <v>552188</v>
       </c>
       <c r="R18" t="n">
-        <v>7063491</v>
+        <v>7063371</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2545,7 +2455,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2555,7 +2465,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,15 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822072</v>
+        <v>119822166</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,16 +2526,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552157</v>
+        <v>552227</v>
       </c>
       <c r="R19" t="n">
-        <v>7063374</v>
+        <v>7063300</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2657,7 +2572,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2667,12 +2582,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,15 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119821980</v>
+        <v>119822321</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2733,16 +2638,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552124</v>
+        <v>552253</v>
       </c>
       <c r="R20" t="n">
-        <v>7063414</v>
+        <v>7063278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2684,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2784,12 +2694,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,15 +2721,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119821609</v>
+        <v>119822341</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,31 +2732,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2865,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552085</v>
+        <v>552254</v>
       </c>
       <c r="R21" t="n">
-        <v>7063478</v>
+        <v>7063276</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,7 +2796,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,7 +2806,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,15 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119821908</v>
+        <v>119822383</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2977,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552131</v>
+        <v>552262</v>
       </c>
       <c r="R22" t="n">
-        <v>7063429</v>
+        <v>7063267</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3012,7 +2903,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3022,7 +2913,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3054,15 +2945,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119821499</v>
+        <v>119821609</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,37 +2956,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552067</v>
+        <v>552085</v>
       </c>
       <c r="R23" t="n">
-        <v>7063476</v>
+        <v>7063478</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3129,7 +3024,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3139,12 +3034,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3171,15 +3061,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822257</v>
+        <v>119821898</v>
       </c>
       <c r="B24" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,11 +3089,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -3220,13 +3101,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552246</v>
+        <v>552193</v>
       </c>
       <c r="R24" t="n">
-        <v>7063284</v>
+        <v>7063214</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3253,19 +3134,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>18:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3280,27 +3151,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119821659</v>
+        <v>119822257</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3308,34 +3174,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552056</v>
+        <v>552246</v>
       </c>
       <c r="R25" t="n">
-        <v>7063498</v>
+        <v>7063284</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3367,7 +3242,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3377,12 +3252,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
